--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68755B7F-9689-4A1A-8DBA-1A4CE930DC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946CFC09-21A0-46AA-A3E5-9C1655734556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{7574F4D5-64B5-4E4F-99D9-1FE25859BFCF}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{0B04D08D-8462-4514-B73C-91FDDBC9181D}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
@@ -56,13 +56,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>职业ID</t>
-  </si>
-  <si>
-    <t>ParentJobId</t>
-  </si>
-  <si>
-    <t>父职业ID(0=基础职业)</t>
+    <t>职业ID(角色ID)</t>
   </si>
   <si>
     <t>Creatable</t>
@@ -74,6 +68,12 @@
     <t>能否在创建角色界面选择</t>
   </si>
   <si>
+    <t>DefaultSpecId</t>
+  </si>
+  <si>
+    <t>建角色时默认解锁并生效的专职ID</t>
+  </si>
+  <si>
     <t>StartLevel</t>
   </si>
   <si>
@@ -86,13 +86,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>名字多语言Key(仅客户端)</t>
-  </si>
-  <si>
-    <t>IconKey</t>
-  </si>
-  <si>
-    <t>图标Addressable Key(仅客户端)</t>
+    <t>职业名多语言Key(仅客户端)</t>
+  </si>
+  <si>
+    <t>SubtitleKey</t>
+  </si>
+  <si>
+    <t>副标题多语言Key(仅客户端)</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -101,10 +101,10 @@
     <t>界面排序(仅客户端)</t>
   </si>
   <si>
-    <t>Job_Placeholder_01</t>
-  </si>
-  <si>
-    <t/>
+    <t>Job_Kyaru</t>
+  </si>
+  <si>
+    <t>Job_Kyaru_Sub</t>
   </si>
 </sst>
 </file>
@@ -488,7 +488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D37496-456F-44A9-8B87-B0186B91D68B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB9AD5C-FAB1-4121-9ECD-B12A995F0F02}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -503,7 +503,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -526,10 +526,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>10</v>
@@ -574,11 +574,11 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
+      <c r="C4" t="b">
         <v>1</v>
+      </c>
+      <c r="D4">
+        <v>101</v>
       </c>
       <c r="E4">
         <v>1</v>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946CFC09-21A0-46AA-A3E5-9C1655734556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461098BA-A389-423A-80AD-50293A524564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{0B04D08D-8462-4514-B73C-91FDDBC9181D}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{0E91A2E1-4768-426E-A5B9-9293DA594AF5}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
@@ -80,19 +80,19 @@
     <t>初始等级(仅服务端)</t>
   </si>
   <si>
-    <t>NameKey</t>
+    <t>Name</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>职业名多语言Key(仅客户端)</t>
-  </si>
-  <si>
-    <t>SubtitleKey</t>
-  </si>
-  <si>
-    <t>副标题多语言Key(仅客户端)</t>
+    <t>职业名-中文原文(仅客户端)</t>
+  </si>
+  <si>
+    <t>Subtitle</t>
+  </si>
+  <si>
+    <t>副标题-中文原文(仅客户端)</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -101,10 +101,10 @@
     <t>界面排序(仅客户端)</t>
   </si>
   <si>
-    <t>Job_Kyaru</t>
-  </si>
-  <si>
-    <t>Job_Kyaru_Sub</t>
+    <t>凯露</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -488,7 +488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB9AD5C-FAB1-4121-9ECD-B12A995F0F02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78E7A53-D781-4303-8E17-72473F9C398B}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitProject\REDIV\ReOnline\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461098BA-A389-423A-80AD-50293A524564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB113C1B-06A3-4D66-9A02-5BA2A1F7BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{0E91A2E1-4768-426E-A5B9-9293DA594AF5}"/>
+    <workbookView xWindow="14610" yWindow="3570" windowWidth="28800" windowHeight="15885" xr2:uid="{0E91A2E1-4768-426E-A5B9-9293DA594AF5}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -86,32 +86,71 @@
     <t>string</t>
   </si>
   <si>
-    <t>职业名-中文原文(仅客户端)</t>
-  </si>
-  <si>
     <t>Subtitle</t>
   </si>
   <si>
-    <t>副标题-中文原文(仅客户端)</t>
-  </si>
-  <si>
     <t>SortOrder</t>
   </si>
   <si>
-    <t>界面排序(仅客户端)</t>
-  </si>
-  <si>
     <t>凯露</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中文原文</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副标题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佩可莉姆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +161,26 @@
     <font>
       <sz val="9"/>
       <name val="Consolas"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -148,12 +207,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,10 +557,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78E7A53-D781-4303-8E17-72473F9C398B}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="14.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,13 +591,13 @@
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -544,7 +623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -561,36 +640,76 @@
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>101</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>101</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>201</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>301</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitProject\REDIV\ReOnline\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB113C1B-06A3-4D66-9A02-5BA2A1F7BE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975FA297-BC50-4706-8C92-96DFE1B38226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14610" yWindow="3570" windowWidth="28800" windowHeight="15885" xr2:uid="{0E91A2E1-4768-426E-A5B9-9293DA594AF5}"/>
+    <workbookView xWindow="0" yWindow="5730" windowWidth="44100" windowHeight="14560" xr2:uid="{72A2EF2E-5024-4684-AE19-24B3570DFF5F}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -56,101 +56,103 @@
     <t>int</t>
   </si>
   <si>
-    <t>职业ID(角色ID)</t>
-  </si>
-  <si>
     <t>Creatable</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
+    <t>StartLevel</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
+  </si>
+  <si>
+    <t>凯露</t>
+  </si>
+  <si>
+    <t>排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartStar</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>MaxStar</t>
+  </si>
+  <si>
+    <t>星级上限。有二觉填6，没二觉填5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Subtitle</t>
+  </si>
+  <si>
+    <t>角色ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>能否在创建角色界面选择</t>
-  </si>
-  <si>
-    <t>DefaultSpecId</t>
-  </si>
-  <si>
-    <t>建角色时默认解锁并生效的专职ID</t>
-  </si>
-  <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>初始等级(仅服务端)</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Subtitle</t>
-  </si>
-  <si>
-    <t>SortOrder</t>
-  </si>
-  <si>
-    <t>凯露</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中文原文</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副标题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>界面排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优衣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>佩可莉姆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建角色时的初始星级</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>角色名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>职业名下面那行小字-中文原文</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,13 +179,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="DengXian"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -207,21 +202,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,160 +554,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78E7A53-D781-4303-8E17-72473F9C398B}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66956751-50A4-4DE4-AB43-7A2156D8F095}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="14.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="15.1640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>101</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>201</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>301</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="2">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975FA297-BC50-4706-8C92-96DFE1B38226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7661BA5D-66B2-4611-B529-F8799640B060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5730" windowWidth="44100" windowHeight="14560" xr2:uid="{72A2EF2E-5024-4684-AE19-24B3570DFF5F}"/>
+    <workbookView xWindow="0" yWindow="6320" windowWidth="44100" windowHeight="14560" xr2:uid="{72A2EF2E-5024-4684-AE19-24B3570DFF5F}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -108,9 +108,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Subtitle</t>
-  </si>
-  <si>
     <t>角色ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -141,18 +138,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>职业名下面那行小字-中文原文</t>
+    <t>优衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +173,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,7 +203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -219,6 +220,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66956751-50A4-4DE4-AB43-7A2156D8F095}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.1640625" style="3" customWidth="1"/>
@@ -563,9 +567,11 @@
     <col min="4" max="4" width="21.5" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="20.4140625" customWidth="1"/>
+    <col min="7" max="7" width="22.58203125" customWidth="1"/>
+    <col min="8" max="8" width="49.58203125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,14 +593,11 @@
       <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -616,14 +619,11 @@
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -637,51 +637,45 @@
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <v>1</v>
       </c>
@@ -697,11 +691,34 @@
       <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterJob.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7661BA5D-66B2-4611-B529-F8799640B060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6320" windowWidth="44100" windowHeight="14560" xr2:uid="{72A2EF2E-5024-4684-AE19-24B3570DFF5F}"/>
+    <workbookView xWindow="0" yWindow="3800" windowWidth="41280" windowHeight="15770" xr2:uid="{72A2EF2E-5024-4684-AE19-24B3570DFF5F}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterJob" sheetId="2" r:id="rId1"/>
